--- a/Config/Excel/PlaceSkillConfig.xlsx
+++ b/Config/Excel/PlaceSkillConfig.xlsx
@@ -15,7 +15,7 @@
     <sheet name="TestConfig" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TestConfig!$A$3:$B$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TestConfig!$A$3:$B$5</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
   <si>
     <t>Id</t>
   </si>
@@ -46,6 +46,9 @@
     <t>Description</t>
   </si>
   <si>
+    <t>Image</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
@@ -58,16 +61,25 @@
     <t>描述</t>
   </si>
   <si>
+    <t>图片名</t>
+  </si>
+  <si>
     <t>回收</t>
   </si>
   <si>
     <t>移动后，将自己和上面那张牌放入弃牌堆</t>
   </si>
   <si>
+    <t>cardRecycle</t>
+  </si>
+  <si>
     <t>复制</t>
   </si>
   <si>
     <t>移动后，将自己变成上面那张牌</t>
+  </si>
+  <si>
+    <t>cardCopy</t>
   </si>
 </sst>
 </file>
@@ -1223,16 +1235,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="3"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="15.7777777777778" customWidth="1"/>
     <col min="2" max="2" width="18.3333333333333" customWidth="1"/>
     <col min="3" max="3" width="19.3240740740741" customWidth="1"/>
     <col min="4" max="4" width="39.8888888888889" customWidth="1"/>
+    <col min="5" max="5" width="25.7962962962963" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1243,61 +1256,76 @@
       <c r="D1" t="s">
         <v>2</v>
       </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4">
-        <v>1</v>
+        <v>10001</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5">
-        <v>2</v>
+        <v>10002</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:B4" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:B5" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
